--- a/human_validation/judge/kor/judge_D020_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S005_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,187 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 학군에서 평소 제 수업 업무 위에 이중언어 사회정서학습 프로그램 도입 업무를 추가해서 왔어요. 그럭저럭 하루하루는 보내고 있는데, 평소와 다르게 계속 긴장되고 기운이 빠지는 느낌이에요. 그리고 원래는 그냥 바로 처리했을 수업 계획이랑 이메일을 미루기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 적응장애 (D020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이 '긴장되고 기운 빠지는' 느낌이 새로운 이중언어 프로그램 도입 시기와 관련해서 대략 언제 처음 시작됐는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 제 정규 업무에 그게 추가된 후 첫 한두 달 안에 제가 저 같지 않다는 느낌이 들기 시작했어요. 그 전에는 평소 업무랑 다른 일들을 꽤 잘 관리하고 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 적응장애 (D020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 두어 달 동안, 거의 매일 예전에 즐기시던 활동에 대한 흥미나 즐거움을 잃었다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 딱히 그런 건 못 느꼈어요. 평소 즐기던 것들에 여전히 흥미가 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 재정이나 건강, 가족처럼 삶의 다른 영역에 대해서도 지나치게 걱정하시나요, 아니면 그 불안하고 긴장되는 느낌이 특히 직장 상황과 관련돼 있는 것 같나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 특히 일이랑 관련돼 있는 것 같아요, 새로 추가된 이중언어 프로그램 도입이랑 평소 수업을 따라가려는 것과요. 다른 모든 것에 대해 폭넓게 걱정하고 있다는 느낌은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 긴장되는 느낌 외에도, 대부분의 날에 슬프거나 기분이 가라앉거나 절망적이라고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 대부분의 날이라고까지는 말 못 할 것 같아요. 직장 상황 때문에 기운이 빠지긴 하는데, 절망적이라고까지 느낀 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이 모든 게 시작된 이후로 자신이 쓸모없다고 느끼거나 스스로에게 지나치게 비판적이 되신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 아니요, 제가 쓸모없다고 느끼거나 그런 식으로 스스로를 몰아붙이지는 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 긴장되고 기운 빠지고 업무가 밀리는 이런 느낌들이 직장이나 개인 생활에서의 업무 수행 능력에 눈에 띄게 영향을 주고 있다고 말씀하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 여전히 수업하고 기본적인 책임은 다하고 있는데, 계획 마감을 놓치거나 미룬 적이 있어요. 그리고 예전에는 제가 확실하게 챙기던 업무들도 동료들이 다시 알려줘야 하는 경우가 생겼어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 두어 달 전에 시작된 이 긴장되고 기운 빠지는 느낌을 총 얼마나 겪고 계신가요? 계속 이어져 온 건가요, 아니면 왔다 갔다 했나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 이제 5개월 정도 됐어요, 학군에서 학년 중간에 그 프로그램 도입 역할을 맡긴 이후로요. 그 이후로 꽤 계속 이어져 왔어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진단명: 적응장애 (D020)
 인구통계: 성별 여성 / 나이 56 / 직업상태 elementary or middle school teacher / 최종학력 대학원 졸업
@@ -575,236 +747,29 @@
 증상 지속 기간: 5 months
 추가 요건: Symptoms must develop within 3 months of the onset of the stressor, Within 6 months of the termination of the stressor or its consequences
 주호소 증상 코드: S081
-배경 서술: 마리아는 학년 중간에 전일제로 수업을 하고 신입 교사들을 멘토링하며 가족 및 지역사회 활동까지 병행하는 와중에, 학교의 새로운 이중언어 사회정서학습 프로그램 도입을 조율해 달라는 요청을 받았다. 처음에는 이 역할을 자신의 가치관의 자연스러운 연장선으로 여기며 푸에르토리코 음악과 미술, 이중언어 교재를 연수 자료에 접목시켰지만, 5개월에 걸쳐 그녀의 스트레스 반응은 수업 계획, 살사의 밤, 수채화 시간, 그리고 교실에서의 평소 자신감을 점점 더 방해하게 되었다. 지장은 제한적이었지만 뚜렷했다. 동료들은 그녀가 마감을 예전만큼 꾸준히 지키지 못한다는 걸 눈치챘고, 그녀 스스로도 평소라면 쉽게 처리했을 업무들을 피하고 있는 자신을 발견했다. 학생들에게 더 이상 영향을 주기 전에 문제를 해결하고 싶었던 마리아는 학군의 근로자 지원 프로그램에 연락했고 정신과 평가를 의뢰받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 학군에서 평소 제 수업 업무 위에 이중언어 사회정서학습 프로그램 도입 업무를 추가해서 왔어요. 그럭저럭 하루하루는 보내고 있는데, 평소와 다르게 계속 긴장되고 기운이 빠지는 느낌이에요. 그리고 원래는 그냥 바로 처리했을 수업 계획이랑 이메일을 미루기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이 '긴장되고 기운 빠지는' 느낌이 새로운 이중언어 프로그램 도입 시기와 관련해서 대략 언제 처음 시작됐는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 제 정규 업무에 그게 추가된 후 첫 한두 달 안에 제가 저 같지 않다는 느낌이 들기 시작했어요. 그 전에는 평소 업무랑 다른 일들을 꽤 잘 관리하고 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 두어 달 동안, 거의 매일 예전에 즐기시던 활동에 대한 흥미나 즐거움을 잃었다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 딱히 그런 건 못 느꼈어요. 평소 즐기던 것들에 여전히 흥미가 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 재정이나 건강, 가족처럼 삶의 다른 영역에 대해서도 지나치게 걱정하시나요, 아니면 그 불안하고 긴장되는 느낌이 특히 직장 상황과 관련돼 있는 것 같나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 특히 일이랑 관련돼 있는 것 같아요, 새로 추가된 이중언어 프로그램 도입이랑 평소 수업을 따라가려는 것과요. 다른 모든 것에 대해 폭넓게 걱정하고 있다는 느낌은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 긴장되는 느낌 외에도, 대부분의 날에 슬프거나 기분이 가라앉거나 절망적이라고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 대부분의 날이라고까지는 말 못 할 것 같아요. 직장 상황 때문에 기운이 빠지긴 하는데, 절망적이라고까지 느낀 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이 모든 게 시작된 이후로 자신이 쓸모없다고 느끼거나 스스로에게 지나치게 비판적이 되신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 아니요, 제가 쓸모없다고 느끼거나 그런 식으로 스스로를 몰아붙이지는 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 긴장되고 기운 빠지고 업무가 밀리는 이런 느낌들이 직장이나 개인 생활에서의 업무 수행 능력에 눈에 띄게 영향을 주고 있다고 말씀하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 여전히 수업하고 기본적인 책임은 다하고 있는데, 계획 마감을 놓치거나 미룬 적이 있어요. 그리고 예전에는 제가 확실하게 챙기던 업무들도 동료들이 다시 알려줘야 하는 경우가 생겼어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 두어 달 전에 시작된 이 긴장되고 기운 빠지는 느낌을 총 얼마나 겪고 계신가요? 계속 이어져 온 건가요, 아니면 왔다 갔다 했나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 이제 5개월 정도 됐어요, 학군에서 학년 중간에 그 프로그램 도입 역할을 맡긴 이후로요. 그 이후로 꽤 계속 이어져 왔어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+배경 서술: 마리아는 학년 중간에 전일제로 수업을 하고 신입 교사들을 멘토링하며 가족 및 지역사회 활동까지 병행하는 와중에, 학교의 새로운 이중언어 사회정서학습 프로그램 도입을 조율해 달라는 요청을 받았다. 처음에는 이 역할을 자신의 가치관의 자연스러운 연장선으로 여기며 푸에르토리코 음악과 미술, 이중언어 교재를 연수 자료에 접목시켰지만, 5개월에 걸쳐 그녀의 스트레스 반응은 수업 계획, 살사의 밤, 수채화 시간, 그리고 교실에서의 평소 자신감을 점점 더 방해하게 되었다. 지장은 제한적이었지만 뚜렷했다. 동료들은 그녀가 마감을 예전만큼 꾸준히 지키지 못한다는 걸 눈치챘고, 그녀 스스로도 평소라면 쉽게 처리했을 업무들을 피하고 있는 자신을 발견했다. 학생들에게 더 이상 영향을 주기 전에 문제를 해결하고 싶었던 마리아는 학군의 근로자 지원 프로그램에 연락했고 정신과 평가를 의뢰받았다.
+표집된 증상 목록:
+  - S081 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
+        </is>
+      </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 적응장애 (D020, ICD: F43.23)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 적응장애 (D020, ICD: F43.23)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 0.5
+체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S005_P002__claude-sonnet-5_kor.xlsx
@@ -733,6 +733,11 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -765,11 +770,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S005_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.6771</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.9062</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.875</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
